--- a/InputData/elec/ETS/Electricity Technology Shareweights.xlsx
+++ b/InputData/elec/ETS/Electricity Technology Shareweights.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23801"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rorvis\Dropbox (Energy InNovation)\My Documents\Energy Policy Solutions\US\Models\eps-us\InputData\elec\ETS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ssy02/Desktop/Postdoc Projects/eps-indonesia-cpl/InputData/elec/ETS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{738849F8-3EF3-4804-8F67-3336470FA6D0}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3EBBC3E-DB29-D040-867B-5A5CA92A14D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{9B08635C-C98A-4192-B8F2-5981CE9EC6E6}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="29040" windowHeight="17640" activeTab="1" xr2:uid="{9B08635C-C98A-4192-B8F2-5981CE9EC6E6}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -281,9 +281,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -321,7 +321,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -427,7 +427,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -569,7 +569,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -578,14 +578,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6422D012-50FD-4D0C-A3BE-19778A6AC198}">
   <dimension ref="A1:B21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -593,77 +593,77 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>34</v>
       </c>
@@ -682,13 +682,13 @@
   <sheetPr>
     <tabColor rgb="FF002060"/>
   </sheetPr>
-  <dimension ref="A1:AF17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AZ17"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="34.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="34.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>18</v>
       </c>
@@ -785,8 +785,68 @@
       <c r="AF1">
         <v>2050</v>
       </c>
+      <c r="AG1">
+        <v>2051</v>
+      </c>
+      <c r="AH1">
+        <v>2052</v>
+      </c>
+      <c r="AI1">
+        <v>2053</v>
+      </c>
+      <c r="AJ1">
+        <v>2054</v>
+      </c>
+      <c r="AK1">
+        <v>2055</v>
+      </c>
+      <c r="AL1">
+        <v>2056</v>
+      </c>
+      <c r="AM1">
+        <v>2057</v>
+      </c>
+      <c r="AN1">
+        <v>2058</v>
+      </c>
+      <c r="AO1">
+        <v>2059</v>
+      </c>
+      <c r="AP1">
+        <v>2060</v>
+      </c>
+      <c r="AQ1">
+        <v>2061</v>
+      </c>
+      <c r="AR1">
+        <v>2062</v>
+      </c>
+      <c r="AS1">
+        <v>2063</v>
+      </c>
+      <c r="AT1">
+        <v>2064</v>
+      </c>
+      <c r="AU1">
+        <v>2065</v>
+      </c>
+      <c r="AV1">
+        <v>2066</v>
+      </c>
+      <c r="AW1">
+        <v>2067</v>
+      </c>
+      <c r="AX1">
+        <v>2068</v>
+      </c>
+      <c r="AY1">
+        <v>2069</v>
+      </c>
+      <c r="AZ1">
+        <v>2070</v>
+      </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -883,8 +943,88 @@
       <c r="AF2">
         <v>1</v>
       </c>
+      <c r="AG2">
+        <f>AF2</f>
+        <v>1</v>
+      </c>
+      <c r="AH2">
+        <f t="shared" ref="AH2:AZ16" si="0">AG2</f>
+        <v>1</v>
+      </c>
+      <c r="AI2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AJ2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AK2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AL2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AM2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AN2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AO2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AP2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AR2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AS2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AT2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AU2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AV2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AW2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AZ2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -981,8 +1121,88 @@
       <c r="AF3">
         <v>1</v>
       </c>
+      <c r="AG3">
+        <f t="shared" ref="AG3:AV17" si="1">AF3</f>
+        <v>1</v>
+      </c>
+      <c r="AH3">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AI3">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AJ3">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AK3">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AL3">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AM3">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AN3">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AO3">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AP3">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AQ3">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AR3">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AS3">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AT3">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AU3">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AV3">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AW3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AX3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AY3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AZ3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1079,8 +1299,88 @@
       <c r="AF4">
         <v>1</v>
       </c>
+      <c r="AG4">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AH4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AI4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AJ4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AK4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AL4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AM4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AN4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AO4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AP4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AQ4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AR4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AS4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AT4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AU4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AV4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AW4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AX4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AY4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AZ4">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -1177,8 +1477,88 @@
       <c r="AF5">
         <v>0</v>
       </c>
+      <c r="AG5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -1275,8 +1655,88 @@
       <c r="AF6">
         <v>1</v>
       </c>
+      <c r="AG6">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AH6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AI6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AJ6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AK6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AL6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AM6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AN6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AO6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AP6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AQ6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AR6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AS6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AT6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AU6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AV6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AW6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AX6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AY6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AZ6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -1373,8 +1833,88 @@
       <c r="AF7">
         <v>1</v>
       </c>
+      <c r="AG7">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AH7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AI7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AJ7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AK7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AL7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AM7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AN7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AO7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AP7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AQ7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AR7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AS7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AT7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AU7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AV7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AW7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AX7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AY7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AZ7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -1471,8 +2011,88 @@
       <c r="AF8">
         <v>1</v>
       </c>
+      <c r="AG8">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AH8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AI8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AJ8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AK8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AL8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AM8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AN8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AO8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AP8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AQ8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AR8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AS8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AT8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AU8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AV8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AW8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AX8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AY8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AZ8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -1569,8 +2189,88 @@
       <c r="AF9">
         <v>1</v>
       </c>
+      <c r="AG9">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AH9">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AI9">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AJ9">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AK9">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AL9">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AM9">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AN9">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AO9">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AP9">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AQ9">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AR9">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AS9">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AT9">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AU9">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AV9">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AW9">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AX9">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AY9">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AZ9">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -1667,8 +2367,88 @@
       <c r="AF10">
         <v>1</v>
       </c>
+      <c r="AG10">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AH10">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AI10">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AJ10">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AK10">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AL10">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AM10">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AN10">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AO10">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AP10">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AQ10">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AR10">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AS10">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AT10">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AU10">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AV10">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AW10">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AX10">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AY10">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AZ10">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -1765,8 +2545,88 @@
       <c r="AF11">
         <v>1</v>
       </c>
+      <c r="AG11">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AH11">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AI11">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AJ11">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AK11">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AL11">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AM11">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AN11">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AO11">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AP11">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AQ11">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AR11">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AS11">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AT11">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AU11">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AV11">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AW11">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AX11">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AY11">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AZ11">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
     </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -1863,8 +2723,88 @@
       <c r="AF12">
         <v>1</v>
       </c>
+      <c r="AG12">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AH12">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AI12">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AJ12">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AK12">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AL12">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AM12">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AN12">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AO12">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AP12">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AQ12">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AR12">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AS12">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AT12">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AU12">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AV12">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AW12">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AX12">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AY12">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AZ12">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -1961,8 +2901,88 @@
       <c r="AF13">
         <v>1</v>
       </c>
+      <c r="AG13">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AH13">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AI13">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AJ13">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AK13">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AL13">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AM13">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AN13">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AO13">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AP13">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AQ13">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AR13">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AS13">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AT13">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AU13">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AV13">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AW13">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AX13">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AY13">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AZ13">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
     </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -2059,8 +3079,88 @@
       <c r="AF14">
         <v>1</v>
       </c>
+      <c r="AG14">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AH14">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AI14">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AJ14">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AK14">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AL14">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AM14">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AN14">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AO14">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AP14">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AQ14">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AR14">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AS14">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AT14">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AU14">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AV14">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AW14">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AX14">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AY14">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="AZ14">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -2157,8 +3257,88 @@
       <c r="AF15">
         <v>0</v>
       </c>
+      <c r="AG15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -2255,8 +3435,88 @@
       <c r="AF16">
         <v>0</v>
       </c>
+      <c r="AG16">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL16">
+        <f t="shared" ref="AH16:AZ17" si="2">AK16</f>
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AN16">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AO16">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AP16">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AQ16">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AR16">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AS16">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AT16">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AU16">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AV16">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AW16">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AX16">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AY16">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AZ16">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="17" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:52" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -2351,6 +3611,86 @@
         <v>1</v>
       </c>
       <c r="AF17">
+        <v>1</v>
+      </c>
+      <c r="AG17">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AH17">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AI17">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AJ17">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AK17">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AL17">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AM17">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AN17">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AO17">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AP17">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AQ17">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AR17">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AS17">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AT17">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AU17">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AV17">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AW17">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AX17">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AY17">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="AZ17">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
